--- a/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
+++ b/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blogs\my-blog\source\THE_THREE_BODY_PROBLEM_Audio_Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C252A0-60CC-4C73-AC1D-1AE4E75D07BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722ADF03-C6D4-4871-ADE6-CA54DF350EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,9 +667,6 @@
     <t>这是一次公众集会，目的是通过言语和身体虐待来羞辱和瓦解革命的敌人，直到他们在群众面前承认他们的罪行。</t>
   </si>
   <si>
-    <t>由于革命者已经分裂成许多派别，各地的敌对势力都参与了复杂的演习和竞赛。在大学内部，红卫兵、文革工作组、工宣队、军宣队之间爆发了激烈的冲突。</t>
-  </si>
-  <si>
     <t>每个派别不时分裂成新的反叛团体，每个团体都有不同的背景和议程，导致更加残酷的战斗。</t>
   </si>
   <si>
@@ -778,6 +775,10 @@
   </si>
   <si>
     <t>但是这种理想的受害者越来越少了。清华大概只剩下一个了。因为他是如此罕见，他被保留到最后的斗争会议。</t>
+  </si>
+  <si>
+    <t>由于革命者分裂成众多派系，各地反对势力展开了复杂的博弈与角逐。在大学内部，红卫兵、文化大革命工作组、工人宣传队和军事宣传队之间爆发了激烈冲突。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1552,6 +1553,12 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>4.2013888888888891E-3</v>
+      </c>
+      <c r="B21" s="1">
+        <v>4.43287037037037E-3</v>
+      </c>
       <c r="C21" s="2" t="s">
         <v>71</v>
       </c>
@@ -1562,10 +1569,16 @@
         <v>85</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>4.43287037037037E-3</v>
+      </c>
+      <c r="B22" s="1">
+        <v>4.5601851851851853E-3</v>
+      </c>
       <c r="C22" s="2" t="s">
         <v>72</v>
       </c>
@@ -1576,10 +1589,16 @@
         <v>86</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>4.5717592592592589E-3</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4.7569444444444447E-3</v>
+      </c>
       <c r="C23" s="2" t="s">
         <v>73</v>
       </c>
@@ -1590,10 +1609,16 @@
         <v>87</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>4.7685185185185183E-3</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4.9884259259259257E-3</v>
+      </c>
       <c r="C24" s="2" t="s">
         <v>74</v>
       </c>
@@ -1604,10 +1629,16 @@
         <v>88</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>4.9884259259259257E-3</v>
+      </c>
+      <c r="B25" s="1">
+        <v>5.324074074074074E-3</v>
+      </c>
       <c r="C25" s="2" t="s">
         <v>75</v>
       </c>
@@ -1618,10 +1649,16 @@
         <v>89</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>5.347222222222222E-3</v>
+      </c>
+      <c r="B26" s="1">
+        <v>5.4861111111111109E-3</v>
+      </c>
       <c r="C26" s="2" t="s">
         <v>76</v>
       </c>
@@ -1632,10 +1669,16 @@
         <v>90</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>5.4861111111111109E-3</v>
+      </c>
+      <c r="B27" s="1">
+        <v>5.6365740740740742E-3</v>
+      </c>
       <c r="C27" s="2" t="s">
         <v>77</v>
       </c>
@@ -1646,10 +1689,16 @@
         <v>91</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>5.6365740740740742E-3</v>
+      </c>
+      <c r="B28" s="1">
+        <v>5.8680555555555552E-3</v>
+      </c>
       <c r="C28" s="2" t="s">
         <v>78</v>
       </c>
@@ -1660,10 +1709,16 @@
         <v>92</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>5.8680555555555552E-3</v>
+      </c>
+      <c r="B29" s="1">
+        <v>6.076388888888889E-3</v>
+      </c>
       <c r="C29" s="2" t="s">
         <v>79</v>
       </c>
@@ -1674,10 +1729,16 @@
         <v>93</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>6.0879629629629626E-3</v>
+      </c>
+      <c r="B30" s="1">
+        <v>6.2847222222222219E-3</v>
+      </c>
       <c r="C30" s="2" t="s">
         <v>80</v>
       </c>
@@ -1688,10 +1749,16 @@
         <v>94</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>6.2962962962962964E-3</v>
+      </c>
+      <c r="B31" s="1">
+        <v>6.4467592592592588E-3</v>
+      </c>
       <c r="C31" s="2" t="s">
         <v>81</v>
       </c>
@@ -1702,7 +1769,7 @@
         <v>95</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
+++ b/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blogs\my-blog\source\THE_THREE_BODY_PROBLEM_Audio_Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722ADF03-C6D4-4871-ADE6-CA54DF350EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7AFA35-4EA8-4A36-AB75-86B472C0AB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
   <si>
     <t>The Red Union had been attacking the headquarters of the April Twenty-eighth Brigade for two days. Their red flags fluttered restlessly around the brigade building like flames yearning for firewood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -778,6 +778,18 @@
   </si>
   <si>
     <t>由于革命者分裂成众多派系，各地反对势力展开了复杂的博弈与角逐。在大学内部，红卫兵、文化大革命工作组、工人宣传队和军事宣传队之间爆发了激烈冲突。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:06:23.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:09:17.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:09:04.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -874,7 +886,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -901,6 +913,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1556,8 +1571,8 @@
       <c r="A21" s="1">
         <v>4.2013888888888891E-3</v>
       </c>
-      <c r="B21" s="1">
-        <v>4.43287037037037E-3</v>
+      <c r="B21" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>71</v>
@@ -1573,8 +1588,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>4.43287037037037E-3</v>
+      <c r="A22" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="B22" s="1">
         <v>4.5601851851851853E-3</v>
@@ -1737,7 +1752,7 @@
         <v>6.0879629629629626E-3</v>
       </c>
       <c r="B30" s="1">
-        <v>6.2847222222222219E-3</v>
+        <v>6.2962962962962964E-3</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>80</v>
@@ -1753,11 +1768,11 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>6.2962962962962964E-3</v>
-      </c>
-      <c r="B31" s="1">
-        <v>6.4467592592592588E-3</v>
+      <c r="A31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>81</v>

--- a/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
+++ b/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blogs\my-blog\source\THE_THREE_BODY_PROBLEM_Audio_Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7AFA35-4EA8-4A36-AB75-86B472C0AB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47333C8B-1EC7-4280-A929-719E2F7E099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,8 +735,42 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>在四十天的时间里，仅在北京，就有一千七百多名斗争会的受害者被打死。许多人选择了一条更容易的道路来避免这种疯狂</t>
+    <t>随着残酷斗争的继续，那些在初期幸存下来的人逐渐变得麻木。保护性的精神外壳帮助他们避免完全崩溃。</t>
+  </si>
+  <si>
+    <t>在治疗过程中，他们经常看起来半睡半醒，只有当有人在他们面前尖叫，让他们机械地背诵他们已经重复了无数次的供词时，他们才会惊醒。</t>
+  </si>
+  <si>
+    <t>然后，他们中的一些人进入了第三阶段。持续不断的斗争会议像水银一样将生动的政治图像注入他们的意识，直到他们建立在知识和理性基础上的头脑在攻击下崩溃。</t>
+  </si>
+  <si>
+    <t>他们开始真正相信他们是有罪的，看到他们如何损害了革命的伟大事业。他们哭了，他们的忏悔远比那些不是知识分子的妖魔鬼怪来得深刻和真诚。</t>
+  </si>
+  <si>
+    <t>对于红卫兵来说，在后两个心理阶段对受害者进行大量虐待是非常无聊的。只有那些仍处于初级阶段的怪物和恶魔才能给他们过度刺激的大脑带来他们渴望的刺激，就像斗牛士的红色斗篷。</t>
+  </si>
+  <si>
+    <t>但是这种理想的受害者越来越少了。清华大概只剩下一个了。因为他是如此罕见，他被保留到最后的斗争会议。</t>
+  </si>
+  <si>
+    <t>由于革命者分裂成众多派系，各地反对势力展开了复杂的博弈与角逐。在大学内部，红卫兵、文化大革命工作组、工人宣传队和军事宣传队之间爆发了激烈冲突。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:06:23.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:09:17.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0:09:04.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在四十多天的时间里，仅在北京就有一千七百多名斗争会的受害者被殴打致死。还有许多人选择了一条更轻松的道路来躲避疯狂：</t>
     </r>
     <r>
       <rPr>
@@ -745,51 +779,19 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>老舍、吴晗、翦伯赞、傅雷、赵九章、易群、文杰、海默和其他曾经受人尊敬的知识分子都选择了结束自己的生命</t>
-    </r>
-  </si>
-  <si>
-    <t>随着残酷斗争的继续，那些在初期幸存下来的人逐渐变得麻木。保护性的精神外壳帮助他们避免完全崩溃。</t>
-  </si>
-  <si>
-    <t>在治疗过程中，他们经常看起来半睡半醒，只有当有人在他们面前尖叫，让他们机械地背诵他们已经重复了无数次的供词时，他们才会惊醒。</t>
-  </si>
-  <si>
-    <t>然后，他们中的一些人进入了第三阶段。持续不断的斗争会议像水银一样将生动的政治图像注入他们的意识，直到他们建立在知识和理性基础上的头脑在攻击下崩溃。</t>
-  </si>
-  <si>
-    <t>他们开始真正相信他们是有罪的，看到他们如何损害了革命的伟大事业。他们哭了，他们的忏悔远比那些不是知识分子的妖魔鬼怪来得深刻和真诚。</t>
-  </si>
-  <si>
-    <t>对于红卫兵来说，在后两个心理阶段对受害者进行大量虐待是非常无聊的。只有那些仍处于初级阶段的怪物和恶魔才能给他们过度刺激的大脑带来他们渴望的刺激，就像斗牛士的红色斗篷。</t>
-  </si>
-  <si>
-    <t>但是这种理想的受害者越来越少了。清华大概只剩下一个了。因为他是如此罕见，他被保留到最后的斗争会议。</t>
-  </si>
-  <si>
-    <t>由于革命者分裂成众多派系，各地反对势力展开了复杂的博弈与角逐。在大学内部，红卫兵、文化大革命工作组、工人宣传队和军事宣传队之间爆发了激烈冲突。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:06:23.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:09:17.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0:09:04.5</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">老舍、吴晗、翦伯赞、傅雷、赵九章、易群、闻捷、海默等曾经受人尊敬的知识分子都选择了结束自己的生命。
+</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -886,7 +888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -917,6 +919,9 @@
     </xf>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1572,7 +1577,7 @@
         <v>4.2013888888888891E-3</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>71</v>
@@ -1584,12 +1589,12 @@
         <v>85</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B22" s="1">
         <v>4.5601851851851853E-3</v>
@@ -1663,8 +1668,8 @@
       <c r="E25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>102</v>
+      <c r="F25" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1684,7 +1689,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1704,7 +1709,7 @@
         <v>91</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1724,7 +1729,7 @@
         <v>92</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1744,7 +1749,7 @@
         <v>93</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1764,15 +1769,15 @@
         <v>94</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>81</v>
@@ -1784,7 +1789,7 @@
         <v>95</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
+++ b/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blogs\my-blog\source\THE_THREE_BODY_PROBLEM_Audio_Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47333C8B-1EC7-4280-A929-719E2F7E099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B5206-17F8-4A84-90F6-D05301ADC61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,9 +735,6 @@
     </r>
   </si>
   <si>
-    <t>随着残酷斗争的继续，那些在初期幸存下来的人逐渐变得麻木。保护性的精神外壳帮助他们避免完全崩溃。</t>
-  </si>
-  <si>
     <t>在治疗过程中，他们经常看起来半睡半醒，只有当有人在他们面前尖叫，让他们机械地背诵他们已经重复了无数次的供词时，他们才会惊醒。</t>
   </si>
   <si>
@@ -793,6 +790,9 @@
 </t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随着残酷斗争的继续，那些在最初阶段幸存下来的人逐渐变得麻木，精神保护壳帮助他们避免了彻底崩溃。</t>
   </si>
 </sst>
 </file>
@@ -888,7 +888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -919,9 +919,6 @@
     </xf>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1577,7 +1574,7 @@
         <v>4.2013888888888891E-3</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>71</v>
@@ -1589,12 +1586,12 @@
         <v>85</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B22" s="1">
         <v>4.5601851851851853E-3</v>
@@ -1668,8 +1665,8 @@
       <c r="E25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>112</v>
+      <c r="F25" s="8" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1689,7 +1686,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1709,7 +1706,7 @@
         <v>91</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1729,7 +1726,7 @@
         <v>92</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1749,7 +1746,7 @@
         <v>93</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1769,15 +1766,15 @@
         <v>94</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>81</v>
@@ -1789,7 +1786,7 @@
         <v>95</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
+++ b/source/THE_THREE_BODY_PROBLEM_Audio_Book/1-1疯狂年代_The_Madness_Years.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Blogs\my-blog\source\THE_THREE_BODY_PROBLEM_Audio_Book\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1B5206-17F8-4A84-90F6-D05301ADC61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E672257F-48A7-480D-A63B-9851514AC2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,19 +735,7 @@
     </r>
   </si>
   <si>
-    <t>在治疗过程中，他们经常看起来半睡半醒，只有当有人在他们面前尖叫，让他们机械地背诵他们已经重复了无数次的供词时，他们才会惊醒。</t>
-  </si>
-  <si>
-    <t>然后，他们中的一些人进入了第三阶段。持续不断的斗争会议像水银一样将生动的政治图像注入他们的意识，直到他们建立在知识和理性基础上的头脑在攻击下崩溃。</t>
-  </si>
-  <si>
     <t>他们开始真正相信他们是有罪的，看到他们如何损害了革命的伟大事业。他们哭了，他们的忏悔远比那些不是知识分子的妖魔鬼怪来得深刻和真诚。</t>
-  </si>
-  <si>
-    <t>对于红卫兵来说，在后两个心理阶段对受害者进行大量虐待是非常无聊的。只有那些仍处于初级阶段的怪物和恶魔才能给他们过度刺激的大脑带来他们渴望的刺激，就像斗牛士的红色斗篷。</t>
-  </si>
-  <si>
-    <t>但是这种理想的受害者越来越少了。清华大概只剩下一个了。因为他是如此罕见，他被保留到最后的斗争会议。</t>
   </si>
   <si>
     <t>由于革命者分裂成众多派系，各地反对势力展开了复杂的博弈与角逐。在大学内部，红卫兵、文化大革命工作组、工人宣传队和军事宣传队之间爆发了激烈冲突。</t>
@@ -793,6 +781,26 @@
   </si>
   <si>
     <t>随着残酷斗争的继续，那些在最初阶段幸存下来的人逐渐变得麻木，精神保护壳帮助他们避免了彻底崩溃。</t>
+  </si>
+  <si>
+    <t>然后，他们中的一些人进入了第三阶段。持续不断的斗争会议像水银一样将生动的政治图像注入他们的意识，直到他们建立在知识和理性基础上的头脑在攻击下崩溃。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在治疗过程中，他们经常看起来半睡半醒，只有当有人在他们面前尖叫，让他们机械地背诵他们已经重复了无数次的供词时，他们才会惊醒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">对于红卫兵来说，在后两个心理阶段对受害者进行大量虐待是非常无聊的。只有那些仍处于初级阶段的怪物和恶魔才能给他们过度刺激的大脑带来他们渴望的刺激，就像斗牛士的红色斗篷。
+对于红卫兵来说，对处于后两个精神阶段的受害者进行虐待是非常无聊的。只有那些仍处于初始阶段的妖魔鬼怪才能给他们过度兴奋的大脑带来他们渴望的刺激，就像斗牛士的红色斗篷一样。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">但是这种理想的受害者越来越少了。清华大概只剩下一个了。因为他是如此罕见，他被保留到最后的斗争会议。
+但这种理想的牺牲品已经越来越少了。在清华，可能只剩下一个了。因为他太稀有了，所以被保留到了斗争会的最后。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -888,7 +896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -919,6 +927,9 @@
     </xf>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1574,7 +1585,7 @@
         <v>4.2013888888888891E-3</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>71</v>
@@ -1586,12 +1597,12 @@
         <v>85</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B22" s="1">
         <v>4.5601851851851853E-3</v>
@@ -1666,7 +1677,7 @@
         <v>89</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1686,7 +1697,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1706,7 +1717,7 @@
         <v>91</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1726,7 +1737,7 @@
         <v>92</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1746,7 +1757,7 @@
         <v>93</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1765,16 +1776,16 @@
       <c r="E30" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>105</v>
+      <c r="F30" s="11" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>81</v>
@@ -1785,8 +1796,8 @@
       <c r="E31" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>106</v>
+      <c r="F31" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
